--- a/templates/KTS-Factuur-template-RevA.xlsx
+++ b/templates/KTS-Factuur-template-RevA.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="164" formatCode="€ #,##0.00"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -31,7 +31,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0007567F"/>
-      <sz val="24"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -68,6 +68,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="000F1B2D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="005C6675"/>
       <sz val="8"/>
     </font>
@@ -79,6 +84,7 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="000F1B2D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -95,14 +101,9 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000F1B2D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0007567F"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -156,50 +157,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -280,12 +304,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="904875" cy="600075"/>
+    <ext cx="209550" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -293,6 +317,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="800100" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -595,22 +644,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FACTUUR</t>
+          <t xml:space="preserve">  FACTUUR</t>
         </is>
       </c>
     </row>
@@ -620,21 +669,16 @@
           <t>AAN</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>[Klantnaam B.V.]</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Nieuwboerweg 2A, 1738BB Waarland</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>[Klantnaam]</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>+31 6 5123 9050  -  info@kuijpers-ts.nl</t>
         </is>
       </c>
     </row>
@@ -644,6 +688,11 @@
           <t>[t.a.v. crediteurenadministratie]</t>
         </is>
       </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>+31 6 5123 9050  ·  info@kuijpers-ts.nl</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -655,18 +704,18 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>[Postbus / Adres]</t>
+          <t>[Postbus 800]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>[Postcode plaats]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="12" customHeight="1">
+          <t>[2800 AB Gouda]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>FACTUURNUMMER</t>
@@ -678,17 +727,17 @@
           <t>FACTUURDATUM</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>VERVALDATUM</t>
+        </is>
+      </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>VERVALDATUM</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
           <t>PROJECT</t>
         </is>
       </c>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -703,291 +752,283 @@
           <t>[DD-MM-JJJJ]</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>[DD-MM-JJJJ]</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>[Projectnaam]</t>
         </is>
       </c>
+      <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Projectnummer</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Opdrachtnummer</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>PO-nummer</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1">
+    <row r="17" ht="12" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Loonheffingennummer KTDS Holding B.V.</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>866381557L01</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="14" customHeight="1">
+    <row r="18" ht="12" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Loonheffingennummer Kuijpers TD Holding B.V.</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>866381594L01</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>PERIODE</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>OMSCHRIJVING</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>AANTAL</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>EENHEID</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>TARIEF</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>SUBTOTAAL</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>BTW%</t>
-        </is>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>BTW %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="19">
+        <f>IFERROR(C21*D21,"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="14">
-        <f>IFERROR(C22*E22,"")</f>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="19">
+        <f>IFERROR(C22*D22,"")</f>
         <v/>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="F22" s="20" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="14">
-        <f>IFERROR(C23*E23,"")</f>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="19">
+        <f>IFERROR(C23*D23,"")</f>
         <v/>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="F23" s="20" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14">
-        <f>IFERROR(C24*E24,"")</f>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="19">
+        <f>IFERROR(C24*D24,"")</f>
         <v/>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="F24" s="20" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="14">
-        <f>IFERROR(C25*E25,"")</f>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="19">
+        <f>IFERROR(C25*D25,"")</f>
         <v/>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="F25" s="20" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="14">
-        <f>IFERROR(C26*E26,"")</f>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="19">
+        <f>IFERROR(C26*D26,"")</f>
         <v/>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="F26" s="20" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14">
-        <f>IFERROR(C27*E27,"")</f>
+    <row r="28">
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>Subtotaal excl. BTW</t>
+        </is>
+      </c>
+      <c r="E28" s="22">
+        <f>SUM(E21:E26)</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="29">
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Subtotaal excl. BTW</t>
-        </is>
-      </c>
-      <c r="F29" s="16">
-        <f>SUM(F22:F27)</f>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>BTW 21%</t>
+        </is>
+      </c>
+      <c r="E29" s="22">
+        <f>E28*0.21</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BTW 21%</t>
-        </is>
-      </c>
-      <c r="F30" s="16">
-        <f>F29*0.21</f>
+    <row r="30" ht="26" customHeight="1">
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>TOTAAL TE BETALEN</t>
+        </is>
+      </c>
+      <c r="E30" s="24">
+        <f>E28+E29</f>
         <v/>
       </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>TOTAAL TE BETALEN</t>
-        </is>
-      </c>
-      <c r="F31" s="18">
-        <f>F29+F30</f>
-        <v/>
-      </c>
+      <c r="F30" s="25" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Wij verzoeken u vriendelijk het totaalbedrag uiterlijk vervaldatum over te maken,</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>onder vermelding van het factuurnummer, naar onderstaande bankrekening:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>IBAN  NL61 BUNQ 2113 3747 30</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>t.n.v. Kuijpers Technical Services BV  -  BIC: BUNQNL2A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>t.n.v. Kuijpers Technical Services BV  ·  BIC: BUNQNL2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>Op deze factuur zijn de Algemene Voorwaarden 2026 van Kuijpers Technical Services BV van toepassing.</t>
         </is>
       </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>KvK 93410557  ·  BTW NL866385368B01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F29:G29"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/templates/KTS-Factuur-template-RevA.xlsx
+++ b/templates/KTS-Factuur-template-RevA.xlsx
@@ -68,13 +68,14 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="005C6675"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="000F1B2D"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005C6675"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -131,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,11 +154,55 @@
         <color rgb="00DCDCDC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCDCDC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCDCDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCDCDC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCDCDC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCDCDC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCDCDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCDCDC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCDCDC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -178,9 +223,20 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -220,6 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -644,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -765,270 +822,324 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
     </row>
-    <row r="14" ht="14" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Projectnummer</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+          <t>KTS-projectcode</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>[KTS2026_XX]</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Projectnummer klant</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Opdrachtnummer</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>PO-nummer</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>PO nummer</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>[Nummer]</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="12" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Loonheffingennummer KTDS Holding B.V.</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>866381557L01</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Loonheffingennummer Kuijpers TD Holding B.V.</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>866381594L01</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>PERIODE</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>OMSCHRIJVING</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>AANTAL</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>TARIEF</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>SUBTOTAAL</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BTW %</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="19">
-        <f>IFERROR(C21*D21,"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="19">
-        <f>IFERROR(C22*D22,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>21</v>
-      </c>
-    </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="19">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22">
         <f>IFERROR(C23*D23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="23" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="19">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22">
         <f>IFERROR(C24*D24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="23" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="19">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22">
         <f>IFERROR(C25*D25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="23" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="19">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22">
         <f>IFERROR(C26*D26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="23" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
-      <c r="D28" s="21" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="22">
+        <f>IFERROR(C27*D27,"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="22">
+        <f>IFERROR(C28*D28,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Subtotaal excl. BTW</t>
         </is>
       </c>
-      <c r="E28" s="22">
-        <f>SUM(E21:E26)</f>
+      <c r="E30" s="25">
+        <f>SUM(E23:E28)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="D29" s="21" t="inlineStr">
+    <row r="31">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>BTW 21%</t>
         </is>
       </c>
-      <c r="E29" s="22">
-        <f>E28*0.21</f>
+      <c r="E31" s="25">
+        <f>E30*0.21</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="D30" s="23" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>TOTAAL TE BETALEN</t>
         </is>
       </c>
-      <c r="E30" s="24">
-        <f>E28+E29</f>
+      <c r="E32" s="27">
+        <f>E30+E31</f>
         <v/>
       </c>
-      <c r="F30" s="25" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="F32" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Wij verzoeken u vriendelijk het totaalbedrag uiterlijk vervaldatum over te maken,</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>onder vermelding van het factuurnummer, naar onderstaande bankrekening:</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>IBAN  NL61 BUNQ 2113 3747 30</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>t.n.v. Kuijpers Technical Services BV  ·  BIC: BUNQNL2A</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>Op deze factuur zijn de Algemene Voorwaarden 2026 van Kuijpers Technical Services BV van toepassing.</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>KvK 93410557  ·  BTW NL866385368B01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E41:G41"/>
+  <mergeCells count="30">
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="D16:G16"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
